--- a/site/exports/scu-arts.xlsx
+++ b/site/exports/scu-arts.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -452,9 +452,9 @@
     <col width="57.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,173 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>艺术学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>当前人事、当前归属与当前职位未知。仅2017旧站团队页支持历史关联，独立教授名录3页未出现此名；不推离职/退休。；三段明确获授，但未另核确切授位日期/授位年或授位法律主体。；两段具名师承不是正式论文导师证明，导师个人身份未另行核。；作品题名存在但没有出版年份，故0书目；不以获奖年替代。；来源差异/限制：历史页的“院长教授”保留为未解析片段，不能建立院长行政职位；另一美术学系副主任陈述仅作历史记录，不定先后或现职。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>艺术学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1027/6952.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>本科/硕士只有学习标签，明确获授未知。；2013美国加利福利亚大学学习的阶段、校区、学位性质和导师不明。；本人导师未知，现时人事未知；独立音乐系目录不等于人事证明。；页面2010日期与后期正文并存，真正更新时间未知。；作品仅见获奖条目，无出版年；不凑数。；来源差异/限制：页面显示2010日期而正文包含后续年份；不推真实更新时间，也不将全文视为2010年时点快照。；来源记载职业信息：职业职称：副教授；硕士生导师。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。；来源记载职业信息：进校年份说明：年份：1996；来源说明：来源只给进校年份，不补岗位、职称晋升年或当前在岗。。上述为留存来源职业表述，不作本轮当前任职或资格认证；指导他人的资格不新增本人导师关系。</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：声乐专业课；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 声乐小组课；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 声乐艺术史概论；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 中国少数民族音乐概论；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 本科毕业论文；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：本科生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 歌唱技巧与演唱风格研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 声乐史论研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 声乐教学研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm | 声乐艺术表演研究；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：硕士研究生；来源主讲课程列表；无学年、学期或当前开课证明。；来源ID：new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03；https://art.scu.edu.cn/info/1027/6952.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>艺术学院</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>现职unknown；目录、历史角色与开放任期不等于观察日人事确认。；仅必要官网职业摘录与书目；未独立核出版元数据或全文。；法律授位实体未独立核验；学习时间与授位时间分开。；目录原始href、页面文本链接导航和浏览器页面导航分别记载，不互相替代。；明确行政教辅兼任本科教学，专任教师false，当前师资计数false；职称unknown，不推教授。；本科和硕士明确获授；5条本科、1条硕士阶段师从仅学习关系，不升级正式论文导师。；导师关系中的两段必要片段来自同一句，分开保留，不恢复省略的非必要信息或伪造连续引文。；未列本人独立作品题名；0作品仅已读范围缺口，不拿课程、临摹碑帖、展览当本人作品。；来源单位：艺术学院 / 发展规划科。本站按“艺术学院”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：书法简史与书法技法基础；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm | 书法；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm | 篆刻；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm | 写生-3（人物）；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm | 楷书临摹；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm | 行书临摹；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；课程列表本身未逐门标明层级；简介另明确兼任本科专业教学。；来源ID：new-recovery-scu-lianchao-calligraphy-s001-f668e085b808；https://art.scu.edu.cn/info/1030/7083.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,12 +800,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26.6" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36.4" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -655,7 +817,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="57.4" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
@@ -720,7 +882,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1005,13 +1167,849 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>文学学士学位</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>西南师范大学</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>明确毕业并获学位；历史学校名称照原文保留。学习区间终年不自动补为授位日期或独立授位年。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科；来源department：美术学院</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>文学硕士学位</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>中国美术史论</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>明确毕业并获学位；历史学校名称照原文保留。学习区间终年不自动补为授位日期或独立授位年。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士；来源department：艺术学院</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>文学博士学位</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>中央美术学院</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>中国美术史论</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>明确毕业并获学位；历史学校名称照原文保留。学习区间终年不自动补为授位日期或独立授位年。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>任教</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>长江大学</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>历史机构名称按来源，未核当年法定名称或改名沿革。；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：艺术学院</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>任教；美术学系副主任</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>至今仅相对于来源陈述；副主任任职起点未披露，不把2007当副主任任职起年。；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：艺术学院美术学系</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>本科</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>四川音乐学院</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>教育标签和学习区间不推明确获授，也不把本科标签改成学士。音乐教育系是部门名，不自动推学位专业。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：音乐教育系</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1027/6952.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>degree_study</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>上海师范大学</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>教育标签和学习区间不推明确获授，也不把本科标签改成学士。音乐教育系是部门名，不自动推学位专业。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：音乐学院</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1027/6952.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>overseas_study_unspecified</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>美国加利福利亚大学</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>只写赴海外学习，未说明访问或非学位，故既不认授位也不标非学位false；不猜加州校区、修正校名或导师。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（event_kind）：overseas_study_unspecified</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1027/6952.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>文学学士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>国画</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2010-06</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>明确2010年6月毕业获文学学士；2006年入学。学位发行法律主体不另推。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：本科</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>文学硕士</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>书法</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>明确2013年6月研究生毕业获文学硕士；同年入学回指2010年，月未知。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2013-07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>留校工作不等该月成为主任或专任教师。；任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>主任</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：艺术学院发展规划办</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>兼任本科书法、国画、美术学等专业教学工作</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：艺术学院</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S5"/>
+  <autoFilter ref="A1:S18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1023,18 +2021,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54.59999999999999" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="57.4" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1102,8 +2100,418 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>黄宗贤</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_studied_under</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；研习师承具有学习阶段；不提升为正式学位论文导师，未另查导师身份。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>金维诺</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>stage_specific_studied_under</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；研习师承具有学习阶段；不提升为正式学位论文导师，未另查导师身份。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>段七丁</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>undergraduate_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学国画本科阶段</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>唐允明</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>undergraduate_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学国画本科阶段</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>巫成金</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>undergraduate_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学国画本科阶段</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>孙林</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>undergraduate_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学国画本科阶段</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>侯开嘉</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>undergraduate_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学国画本科阶段</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>李晟</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>masters_stage_learning_mentorship</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学书法研究生阶段</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；官网学习阶段师从措辞；不是正式学位论文导师证据。未从学习前人的作品推师承。；两段来自同一原文相关位置师从句，省略非必要亲缘修饰；不伪造连续原句。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L9"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1325,14 +2733,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="23.8" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="57.4" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1440,11 +2848,315 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-hangang-art-history-s001-b7f7a01e9abf</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1158/8061.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:57:26Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-hangang-art-history-s002-eb2812fe40e5</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/xygk/szdw/js/2.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:57:57Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-hangang-art-history-s003-7db98233854e</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/xygk/szdw/js.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:58:01Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>韩刚</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-hangang-art-history-s004-e3fdf869e8df</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/xygk/szdw/js/1.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:58:04Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-huangying-vocal-music-s001-0d8405403bb3</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/xygk/szdw/fjs.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:59:10Z</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>黄英</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-huangying-vocal-music-s002-c55ac2f52f03</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1027/6952.htm</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T22:59:49Z</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-lianchao-calligraphy-s001-f668e085b808</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/info/1030/7083.htm</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:23:37.674Z</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>连超</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-scu-lianchao-calligraphy-s002-ecfcbbf9dd70</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://art.scu.edu.cn/xygk/szdw/xzjf.htm</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T03:23:45.880Z</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>scu</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>四川大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/scu-arts.xlsx
+++ b/site/exports/scu-arts.xlsx
@@ -1275,7 +1275,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="b">
@@ -1722,7 +1722,7 @@
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L14" s="2" t="b">
@@ -1797,7 +1797,7 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L15" s="2" t="b">
